--- a/Treinamento/New folder/EmissaoFielDepositario.xlsx
+++ b/Treinamento/New folder/EmissaoFielDepositario.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{EBDD466B-D3C0-4A55-975C-84995C275EEE}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B7D0DA-5685-47F4-9C54-6869A98FD75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15840" windowWidth="29040" xWindow="20370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="FIEL" r:id="rId1" sheetId="1"/>
-    <sheet name="P3" r:id="rId2" sheetId="2"/>
+    <sheet name="FIEL" sheetId="1" r:id="rId1"/>
+    <sheet name="P3" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">FIEL!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FIEL!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2805" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="60">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -100,15 +100,6 @@
     <t>20/9/2025</t>
   </si>
   <si>
-    <t>Alerte: Proposta Não Liberada!</t>
-  </si>
-  <si>
-    <t>Alerta: Liberação não efetuada!</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
     <t>5177-2025-35-11-0014233/ 0</t>
   </si>
   <si>
@@ -131,12 +122,6 @@
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>Alerta:  A apólice não é bloqueada</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>5177-2025-12-11-0014238/ 0</t>
@@ -230,7 +215,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -295,42 +279,42 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="1" xr:uid="{9A64B6ED-0441-41B2-A6F4-AEA4AC2561AE}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -347,10 +331,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -385,7 +369,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -437,7 +421,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -548,21 +532,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -579,7 +563,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -631,36 +615,36 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:P205"/>
+  <dimension ref="A1:O205"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="13.7109375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="5" width="23.42578125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="5" width="35.85546875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="5" width="24.5703125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="5" width="21.28515625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="8" width="48.42578125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="8" width="32.28515625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="5" width="24.28515625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="5" width="18.42578125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="5" width="17.85546875" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="5" width="16.7109375" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="5" width="19.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="41.42578125" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="1" width="56.0" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="1" width="28.42578125" collapsed="true"/>
-    <col min="16" max="16384" style="5" width="9.140625" collapsed="true"/>
+    <col min="1" max="1" width="13.7109375" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="23.42578125" style="5" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.85546875" style="5" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.5703125" style="5" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="21.28515625" style="5" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="48.42578125" style="8" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="32.28515625" style="8" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="24.28515625" style="5" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="18.42578125" style="5" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="17.85546875" style="5" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="16.7109375" style="5" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="19" style="5" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="41.42578125" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="56" style="1" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="28.42578125" style="1" customWidth="1" collapsed="1"/>
+    <col min="16" max="16384" width="9.140625" style="5" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -736,13 +720,13 @@
         <v>61</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -771,13 +755,13 @@
         <v>61</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O3" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -806,13 +790,13 @@
         <v>61</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -841,13 +825,13 @@
         <v>61</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -876,13 +860,13 @@
         <v>61</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O6" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -911,13 +895,13 @@
         <v>61</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -946,13 +930,13 @@
         <v>61</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -981,13 +965,13 @@
         <v>61</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1016,13 +1000,13 @@
         <v>61</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1051,13 +1035,13 @@
         <v>61</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1086,13 +1070,13 @@
         <v>61</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O12" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1121,13 +1105,13 @@
         <v>61</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1156,13 +1140,13 @@
         <v>61</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1191,13 +1175,13 @@
         <v>61</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1226,13 +1210,13 @@
         <v>61</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O16" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -1261,13 +1245,13 @@
         <v>61</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1296,13 +1280,13 @@
         <v>61</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1331,13 +1315,13 @@
         <v>61</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -1366,13 +1350,13 @@
         <v>61</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1401,13 +1385,13 @@
         <v>61</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1436,13 +1420,13 @@
         <v>61</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -1471,13 +1455,13 @@
         <v>61</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1506,13 +1490,13 @@
         <v>61</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1541,13 +1525,13 @@
         <v>61</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -1576,13 +1560,13 @@
         <v>61</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -1611,13 +1595,13 @@
         <v>61</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -1646,13 +1630,13 @@
         <v>61</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -1681,13 +1665,13 @@
         <v>61</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -1716,13 +1700,13 @@
         <v>61</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -1751,13 +1735,13 @@
         <v>61</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -1786,13 +1770,13 @@
         <v>61</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -1821,13 +1805,13 @@
         <v>61</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -1856,13 +1840,13 @@
         <v>61</v>
       </c>
       <c r="M34" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -1891,13 +1875,13 @@
         <v>61</v>
       </c>
       <c r="M35" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -1926,13 +1910,11 @@
         <v>61</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="N36" s="5" t="s">
-        <v>34</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -7177,51 +7159,51 @@
   </sheetData>
   <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
-  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <headerFooter>
-    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></oddFooter>
-    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></evenFooter>
-    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FPÚBLICO]]></firstFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</oddFooter>
+    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</evenFooter>
+    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FPÚBLICO</firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0D0BED-8A1E-40E5-9E38-0B4586E94A24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0D0BED-8A1E-40E5-9E38-0B4586E94A24}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <pageMargins bottom="0.78740157499999996" footer="0.31496062000000002" header="0.31496062000000002" left="0.511811024" right="0.511811024" top="0.78740157499999996"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/New folder/EmissaoFielDepositario.xlsx
+++ b/Treinamento/New folder/EmissaoFielDepositario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B7D0DA-5685-47F4-9C54-6869A98FD75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B7F052-BC70-41E5-AED8-8446710CD325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="61">
   <si>
     <t>PREMIO TOTAL</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>5177-2025-12-11-0014266/ 0</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -1914,7 +1917,7 @@
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -7179,31 +7182,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MjkvMDEvMjAyMCAxNDozODo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAyOS8wMS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32DD15A-9FF0-48CC-8490-4CEC075A995A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{154F03D6-410E-44CD-A5AB-095672E0E5C4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>